--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/VSnull</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -609,7 +609,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>1490: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - MYCOLOGY RPT STATUS (#63.05-19)</t>
+    <t>1490: terminologyMaps using null on MICROBIOLOGY - MYCOLOGY RPT STATUS (#63.05-19)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MycologyReportStatus</t>
@@ -713,7 +713,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1527: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL</t>
+    <t>1527: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1814,7 +1814,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1830,7 +1830,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="226.3125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="247.3984375" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSnull</t>
+    <t>http://va.gov/fhir/ValueSet/VSundefined</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSundefined</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1527: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
+    <t>1527: fixed value = http://loinc.org#42804-5 Fungus identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1830,7 +1830,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="247.3984375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="598">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -892,9 +892,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
-  </si>
-  <si>
-    <t>1527: fixed value = http://loinc.org#42804-5 Fungus identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -2242,7 +2239,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -5394,36 +5391,36 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AQ25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5544,10 +5541,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5670,10 +5667,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5696,19 +5693,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5757,7 +5754,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5772,22 +5769,22 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5798,10 +5795,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5922,10 +5919,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6048,10 +6045,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6077,16 +6074,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6135,7 +6132,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6150,22 +6147,22 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6176,10 +6173,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6205,13 +6202,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6261,7 +6258,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6288,10 +6285,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6302,10 +6299,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6331,14 +6328,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6387,7 +6384,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6402,22 +6399,22 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6428,10 +6425,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6457,14 +6454,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6513,7 +6510,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6528,22 +6525,22 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6554,10 +6551,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6580,19 +6577,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6641,7 +6638,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6668,10 +6665,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6682,10 +6679,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6711,16 +6708,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6769,7 +6766,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6796,10 +6793,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6810,10 +6807,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6836,19 +6833,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6897,7 +6894,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6912,25 +6909,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6938,10 +6935,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6964,16 +6961,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7023,7 +7020,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7050,13 +7047,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7064,14 +7061,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7090,19 +7087,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7151,7 +7148,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7172,19 +7169,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AN39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7192,14 +7189,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7218,19 +7215,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7267,7 +7264,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7277,7 +7274,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7286,31 +7283,31 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AJ40" t="s" s="2">
+      <c r="AK40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AK40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AN40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7318,16 +7315,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="B41" t="s" s="2">
+      <c r="D41" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7346,19 +7343,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7407,7 +7404,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7416,31 +7413,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AJ41" t="s" s="2">
+      <c r="AK41" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AK41" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7448,10 +7445,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7474,16 +7471,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7533,7 +7530,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7548,25 +7545,25 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7574,10 +7571,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7600,17 +7597,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7659,7 +7656,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7674,25 +7671,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AP43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7700,10 +7697,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7726,19 +7723,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7787,7 +7784,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7796,42 +7793,42 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AJ44" t="s" s="2">
+      <c r="AK44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AK44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7857,16 +7854,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7895,7 +7892,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7913,7 +7910,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7922,7 +7919,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7943,7 +7940,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7954,14 +7951,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7983,16 +7980,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8020,11 +8017,11 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8041,7 +8038,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8065,27 +8062,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8108,19 +8105,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8169,7 +8166,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8184,22 +8181,22 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8210,10 +8207,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8239,13 +8236,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8271,14 +8268,14 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>468</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8295,7 +8292,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8319,27 +8316,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8365,16 +8362,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8399,14 +8396,14 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8423,7 +8420,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8450,10 +8447,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8464,10 +8461,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8490,16 +8487,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8549,7 +8546,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8564,36 +8561,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>492</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8616,16 +8613,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8675,7 +8672,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8699,27 +8696,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>501</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8742,19 +8739,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8803,7 +8800,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8815,25 +8812,25 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8844,10 +8841,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8968,10 +8965,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9094,14 +9091,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9123,10 +9120,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9181,7 +9178,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9222,10 +9219,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9248,13 +9245,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9305,7 +9302,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9314,7 +9311,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9332,10 +9329,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9346,10 +9343,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9372,13 +9369,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9429,7 +9426,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9438,7 +9435,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9456,10 +9453,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9470,10 +9467,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9499,16 +9496,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9536,11 +9533,11 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9557,7 +9554,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9581,13 +9578,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>537</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9598,10 +9595,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9627,16 +9624,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9661,14 +9658,14 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9685,7 +9682,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9709,13 +9706,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>537</v>
-      </c>
       <c r="AP59" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9726,10 +9723,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9752,17 +9749,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9811,7 +9808,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9841,7 +9838,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9852,10 +9849,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9881,10 +9878,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9935,7 +9932,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9962,10 +9959,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9976,10 +9973,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10002,16 +9999,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10061,7 +10058,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10088,10 +10085,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10102,10 +10099,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10128,16 +10125,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10187,7 +10184,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10214,10 +10211,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10228,10 +10225,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10254,19 +10251,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10315,7 +10312,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10342,10 +10339,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10356,10 +10353,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10480,10 +10477,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10606,14 +10603,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10635,10 +10632,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10693,7 +10690,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10734,10 +10731,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10763,13 +10760,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>278</v>
@@ -10797,10 +10794,10 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>280</v>
@@ -10821,7 +10818,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10845,16 +10842,16 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AO68" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -10862,10 +10859,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10888,19 +10885,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="N69" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="O69" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10949,7 +10946,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10973,27 +10970,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AO69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AP69" t="s" s="2">
+      <c r="AQ69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR69" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11019,16 +11016,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="N70" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="O70" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11056,10 +11053,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11077,7 +11074,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11086,7 +11083,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11107,7 +11104,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11118,14 +11115,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11147,16 +11144,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11184,11 +11181,11 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11205,7 +11202,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11229,27 +11226,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AO71" t="s" s="2">
+      <c r="AP71" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AP71" t="s" s="2">
+      <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11275,16 +11272,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="N72" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11333,7 +11330,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11360,10 +11357,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,7 +1106,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1291,7 +1291,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1519,7 +1519,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologySpecimen)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,7 +1106,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="599">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1382,6 +1382,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -7925,7 +7928,7 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -7940,7 +7943,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7951,14 +7954,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7980,16 +7983,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8017,10 +8020,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8038,7 +8041,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8062,27 +8065,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8105,19 +8108,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8166,7 +8169,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8181,10 +8184,10 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8193,10 +8196,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8207,10 +8210,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8236,13 +8239,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8268,13 +8271,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8292,7 +8295,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8316,27 +8319,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8362,16 +8365,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8396,13 +8399,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8420,7 +8423,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8447,10 +8450,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8461,10 +8464,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8487,16 +8490,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8546,7 +8549,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8561,36 +8564,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8613,16 +8616,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8672,7 +8675,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8696,27 +8699,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8739,19 +8742,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8800,7 +8803,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8812,7 +8815,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8827,10 +8830,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8841,10 +8844,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8965,10 +8968,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9091,14 +9094,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9120,10 +9123,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9178,7 +9181,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9219,10 +9222,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9245,13 +9248,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9302,7 +9305,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9311,7 +9314,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9329,10 +9332,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9343,10 +9346,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9369,13 +9372,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9426,7 +9429,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9435,7 +9438,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9453,10 +9456,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9467,10 +9470,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9496,16 +9499,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9533,10 +9536,10 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9554,7 +9557,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9578,13 +9581,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9595,10 +9598,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9624,16 +9627,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9658,13 +9661,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9682,7 +9685,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9706,13 +9709,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9723,10 +9726,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9749,17 +9752,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9808,7 +9811,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9838,7 +9841,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9849,10 +9852,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9878,10 +9881,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9932,7 +9935,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9959,10 +9962,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9973,10 +9976,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9999,16 +10002,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10058,7 +10061,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10085,10 +10088,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10099,10 +10102,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10125,16 +10128,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10184,7 +10187,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10211,10 +10214,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10225,10 +10228,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10251,19 +10254,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10312,7 +10315,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10339,10 +10342,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10353,10 +10356,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10477,10 +10480,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10603,14 +10606,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10632,10 +10635,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10690,7 +10693,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10731,10 +10734,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10760,13 +10763,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>278</v>
@@ -10794,10 +10797,10 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>280</v>
@@ -10818,7 +10821,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10842,7 +10845,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>283</v>
@@ -10859,10 +10862,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10888,13 +10891,13 @@
         <v>420</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>424</v>
@@ -10946,7 +10949,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10970,7 +10973,7 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>428</v>
@@ -10987,10 +10990,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11016,13 +11019,13 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>435</v>
@@ -11053,7 +11056,7 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>436</v>
@@ -11074,7 +11077,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11083,7 +11086,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11104,7 +11107,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11115,14 +11118,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11144,16 +11147,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11181,10 +11184,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11202,7 +11205,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11226,27 +11229,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11272,16 +11275,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11330,7 +11333,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11357,10 +11360,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1384,7 +1384,7 @@
 us-core-2</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2031: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/LabObservationStatus</t>
   </si>
   <si>
     <t>1490: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - MYCOLOGY RPT STATUS (63.05-19)</t>
@@ -2232,7 +2232,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="600">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -971,6 +971,10 @@
   </si>
   <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+LabObservationMicrobiologyMycologyObservation-1480-1:if Not NULL then fixed value http://loinc.org {null}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
@@ -6147,10 +6151,10 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6162,10 +6166,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6176,10 +6180,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6205,13 +6209,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6261,7 +6265,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6288,10 +6292,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6302,10 +6306,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6331,14 +6335,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6387,7 +6391,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6402,7 +6406,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6414,10 +6418,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6428,10 +6432,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6457,14 +6461,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6513,7 +6517,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6528,7 +6532,7 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6540,10 +6544,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6554,10 +6558,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6580,19 +6584,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6641,7 +6645,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6668,10 +6672,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6682,10 +6686,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6711,16 +6715,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6769,7 +6773,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6796,10 +6800,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6810,10 +6814,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6836,19 +6840,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6897,7 +6901,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6912,25 +6916,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6938,10 +6942,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6964,16 +6968,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7023,7 +7027,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7053,10 +7057,10 @@
         <v>283</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7064,14 +7068,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7090,19 +7094,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7151,7 +7155,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7172,19 +7176,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7192,14 +7196,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7218,19 +7222,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7267,7 +7271,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7277,7 +7281,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7286,10 +7290,10 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7298,19 +7302,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7318,16 +7322,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7346,19 +7350,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7407,7 +7411,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7416,31 +7420,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7448,10 +7452,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7474,16 +7478,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7533,7 +7537,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7548,10 +7552,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7560,13 +7564,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7574,10 +7578,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7600,17 +7604,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7659,7 +7663,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7674,25 +7678,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7700,10 +7704,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7726,19 +7730,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7787,7 +7791,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7796,10 +7800,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7811,27 +7815,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7857,16 +7861,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7895,7 +7899,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7913,7 +7917,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7922,13 +7926,13 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -7943,7 +7947,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7954,14 +7958,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7983,16 +7987,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8020,10 +8024,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8041,7 +8045,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8065,27 +8069,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8108,19 +8112,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8169,7 +8173,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8184,10 +8188,10 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8196,10 +8200,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8210,10 +8214,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8239,13 +8243,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8271,13 +8275,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8295,7 +8299,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8319,27 +8323,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8365,16 +8369,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8399,13 +8403,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8423,7 +8427,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8450,10 +8454,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8464,10 +8468,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8490,16 +8494,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8549,7 +8553,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8564,36 +8568,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8616,16 +8620,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8675,7 +8679,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8699,27 +8703,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8742,19 +8746,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8803,7 +8807,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8815,7 +8819,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8830,10 +8834,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8844,10 +8848,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8968,10 +8972,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9094,14 +9098,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9123,10 +9127,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9181,7 +9185,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9222,10 +9226,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9248,13 +9252,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9305,7 +9309,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9314,7 +9318,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9332,10 +9336,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9346,10 +9350,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9372,13 +9376,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9429,7 +9433,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9438,7 +9442,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9456,10 +9460,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9470,10 +9474,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9499,16 +9503,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9536,10 +9540,10 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9557,7 +9561,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9581,13 +9585,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9598,10 +9602,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9627,16 +9631,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9661,13 +9665,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9685,7 +9689,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9709,13 +9713,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9726,10 +9730,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9752,17 +9756,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9811,7 +9815,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9841,7 +9845,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9852,10 +9856,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9881,10 +9885,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9935,7 +9939,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9962,10 +9966,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9976,10 +9980,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10002,16 +10006,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10061,7 +10065,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10088,10 +10092,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10102,10 +10106,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10128,16 +10132,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10187,7 +10191,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10214,10 +10218,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10228,10 +10232,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10254,19 +10258,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10315,7 +10319,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10342,10 +10346,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10356,10 +10360,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10480,10 +10484,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10606,14 +10610,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10635,10 +10639,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10693,7 +10697,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10734,10 +10738,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10763,13 +10767,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>278</v>
@@ -10797,10 +10801,10 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>280</v>
@@ -10821,7 +10825,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10845,7 +10849,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>283</v>
@@ -10862,10 +10866,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10888,19 +10892,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10949,7 +10953,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10973,27 +10977,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11019,16 +11023,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11056,10 +11060,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11077,7 +11081,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11086,7 +11090,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11107,7 +11111,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11118,14 +11122,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11147,16 +11151,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11184,10 +11188,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11205,7 +11209,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11229,27 +11233,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11275,16 +11279,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11333,7 +11337,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11360,10 +11364,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -974,7 +974,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-LabObservationMicrobiologyMycologyObservation-1480-1:if Not NULL then fixed value http://loinc.org {null}</t>
+lommo-45-1480-1:undefined: if Not NULL then http://loinc.org {null}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org case Not NULL</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1135,7 +1135,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2255,7 +2255,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -807,6 +807,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.MycologyReportStatus</t>
+  </si>
+  <si>
+    <t>Documents.DocumentCompletionStatus,LabOrder.Result.ResultStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1135,8 +1138,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1290,6 +1292,9 @@
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
   </si>
   <si>
+    <t>Documents.ToTime,LabOrder.Result.ResultTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1321,6 +1326,9 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
+    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1550,6 +1558,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
+  </si>
+  <si>
+    <t>LabOrder.ResultExtension.GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2255,7 +2266,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -5091,22 +5102,22 @@
         <v>254</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -5114,10 +5125,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5143,16 +5154,16 @@
         <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>85</v>
@@ -5162,7 +5173,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5180,16 +5191,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5199,7 +5210,7 @@
         <v>171</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5214,7 +5225,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>85</v>
@@ -5232,10 +5243,10 @@
         <v>85</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5243,13 +5254,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5274,16 +5285,16 @@
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5293,7 +5304,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5311,10 +5322,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5332,7 +5343,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5365,10 +5376,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -5376,14 +5387,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5405,16 +5416,16 @@
         <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5442,10 +5453,10 @@
         <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -5463,7 +5474,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>95</v>
@@ -5487,30 +5498,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5634,10 +5645,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5763,10 +5774,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5789,19 +5800,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -5850,7 +5861,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5865,7 +5876,7 @@
         <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -5880,10 +5891,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -5894,10 +5905,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6021,10 +6032,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6150,10 +6161,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6179,16 +6190,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6237,7 +6248,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6249,10 +6260,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6267,10 +6278,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6281,10 +6292,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6310,13 +6321,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6366,7 +6377,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6396,10 +6407,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6410,10 +6421,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6439,14 +6450,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6495,7 +6506,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6510,7 +6521,7 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6525,10 +6536,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6539,10 +6550,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6568,14 +6579,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6624,7 +6635,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6639,7 +6650,7 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6654,10 +6665,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6668,10 +6679,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6694,19 +6705,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6755,7 +6766,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6785,10 +6796,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6799,10 +6810,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6828,16 +6839,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6886,7 +6897,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6916,10 +6927,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -6930,10 +6941,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6956,19 +6967,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7017,7 +7028,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7032,28 +7043,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7061,10 +7072,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7087,16 +7098,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7146,7 +7157,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7176,13 +7187,13 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7190,14 +7201,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7216,19 +7227,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7277,7 +7288,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7301,19 +7312,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7321,14 +7332,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7347,19 +7358,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7396,7 +7407,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7406,7 +7417,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7415,10 +7426,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7430,19 +7441,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7450,16 +7461,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7478,19 +7489,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7539,7 +7550,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7548,34 +7559,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7583,10 +7594,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7609,16 +7620,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7668,7 +7679,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7683,13 +7694,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>85</v>
+        <v>409</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7698,13 +7709,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7712,10 +7723,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7738,17 +7749,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7797,7 +7808,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7812,28 +7823,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7841,10 +7852,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7867,19 +7878,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7928,7 +7939,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7937,10 +7948,10 @@
         <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>85</v>
@@ -7955,27 +7966,27 @@
         <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8001,16 +8012,16 @@
         <v>184</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8039,7 +8050,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>85</v>
@@ -8057,7 +8068,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8066,13 +8077,13 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>85</v>
@@ -8090,7 +8101,7 @@
         <v>138</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -8101,14 +8112,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8130,16 +8141,16 @@
         <v>184</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8167,10 +8178,10 @@
         <v>189</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -8188,7 +8199,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8215,27 +8226,27 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8258,19 +8269,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8319,7 +8330,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8334,10 +8345,10 @@
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>85</v>
@@ -8349,10 +8360,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8363,10 +8374,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8392,13 +8403,13 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8424,13 +8435,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8448,7 +8459,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8475,27 +8486,27 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8521,16 +8532,16 @@
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8555,13 +8566,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8579,7 +8590,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8609,10 +8620,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8623,10 +8634,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8649,16 +8660,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8708,7 +8719,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8723,39 +8734,39 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>85</v>
+        <v>495</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8778,16 +8789,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8837,7 +8848,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8864,27 +8875,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8907,19 +8918,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -8968,7 +8979,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8980,7 +8991,7 @@
         <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>85</v>
@@ -8998,10 +9009,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9012,10 +9023,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9139,10 +9150,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9268,14 +9279,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9297,10 +9308,10 @@
         <v>141</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>144</v>
@@ -9355,7 +9366,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9399,10 +9410,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9425,13 +9436,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9482,7 +9493,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9491,7 +9502,7 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
@@ -9512,10 +9523,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9526,10 +9537,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9552,13 +9563,13 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9609,7 +9620,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9618,7 +9629,7 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
@@ -9639,10 +9650,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9653,10 +9664,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9682,16 +9693,16 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
@@ -9719,10 +9730,10 @@
         <v>119</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9740,7 +9751,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9767,13 +9778,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9784,10 +9795,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9813,16 +9824,16 @@
         <v>184</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9847,13 +9858,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -9871,7 +9882,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9898,13 +9909,13 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9915,10 +9926,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9941,17 +9952,17 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10000,7 +10011,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10033,7 +10044,7 @@
         <v>85</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10044,10 +10055,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10073,10 +10084,10 @@
         <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10127,7 +10138,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10157,10 +10168,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10171,10 +10182,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10197,16 +10208,16 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10256,7 +10267,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10286,10 +10297,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10300,10 +10311,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10326,16 +10337,16 @@
         <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10385,7 +10396,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10415,10 +10426,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10429,10 +10440,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10455,19 +10466,19 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10516,7 +10527,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10546,10 +10557,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10560,10 +10571,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10687,10 +10698,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10816,14 +10827,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10845,10 +10856,10 @@
         <v>141</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>144</v>
@@ -10903,7 +10914,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -10947,10 +10958,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10976,16 +10987,16 @@
         <v>184</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11010,31 +11021,31 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>95</v>
@@ -11061,16 +11072,16 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>85</v>
@@ -11078,10 +11089,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11104,19 +11115,19 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11165,7 +11176,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11192,27 +11203,27 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11238,16 +11249,16 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11275,28 +11286,28 @@
         <v>189</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11305,7 +11316,7 @@
         <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>107</v>
@@ -11329,7 +11340,7 @@
         <v>138</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11340,14 +11351,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11369,16 +11380,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11406,10 +11417,10 @@
         <v>189</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11427,7 +11438,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11454,27 +11465,27 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11500,16 +11511,16 @@
         <v>86</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11558,7 +11569,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11588,10 +11599,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1138,7 +1138,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1326,7 +1326,7 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
-    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+    <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1560,7 +1560,7 @@
     <t>Micro.Microbiology.MicrobiologyAccession</t>
   </si>
   <si>
-    <t>LabOrder.ResultExtension.GroupName</t>
+    <t>LabOrder.Extension[ResultExtension].GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2266,7 +2266,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="615">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1307,7 +1307,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1320,6 +1320,47 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-at</t>
+  </si>
+  <si>
+    <t>va-at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
+</t>
+  </si>
+  <si>
+    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
+  </si>
+  <si>
+    <t>Documents.EnteredAt,LabOrder.Result.EnteredAt</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-by</t>
+  </si>
+  <si>
+    <t>va-by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+</t>
+  </si>
+  <si>
     <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
@@ -1327,18 +1368,6 @@
   </si>
   <si>
     <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -2226,7 +2255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS72"/>
+  <dimension ref="A1:AS74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -7740,7 +7769,7 @@
         <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>85</v>
@@ -7796,16 +7825,14 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>413</v>
@@ -7823,28 +7850,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AR43" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7852,12 +7879,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
       </c>
@@ -7878,19 +7907,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7939,56 +7966,58 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AL44" t="s" s="2">
-        <v>85</v>
+        <v>426</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>85</v>
+        <v>427</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>433</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>85</v>
+        <v>421</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
       </c>
@@ -8006,22 +8035,20 @@
         <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>184</v>
+        <v>430</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8046,11 +8073,13 @@
         <v>85</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>85</v>
@@ -8068,43 +8097,43 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>443</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>85</v>
+        <v>432</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>85</v>
+        <v>433</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>138</v>
+        <v>419</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>85</v>
+        <v>421</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8112,45 +8141,45 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>184</v>
+        <v>435</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8175,13 +8204,13 @@
         <v>85</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>453</v>
+        <v>85</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -8199,19 +8228,19 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>107</v>
+        <v>441</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8226,27 +8255,27 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>457</v>
+        <v>445</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8257,7 +8286,7 @@
         <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>96</v>
@@ -8269,19 +8298,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>459</v>
+        <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8306,13 +8335,11 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>85</v>
+        <v>451</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8330,25 +8357,25 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>85</v>
+        <v>452</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>85</v>
@@ -8360,10 +8387,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>466</v>
+        <v>138</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8374,21 +8401,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>85</v>
@@ -8403,15 +8430,17 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8435,13 +8464,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>472</v>
+        <v>189</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8459,13 +8488,13 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>85</v>
@@ -8486,27 +8515,27 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8517,10 +8546,10 @@
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>85</v>
@@ -8529,19 +8558,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>184</v>
+        <v>468</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8566,13 +8595,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>472</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>485</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8590,13 +8619,13 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>85</v>
@@ -8605,10 +8634,10 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>85</v>
+        <v>473</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>85</v>
+        <v>474</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8620,10 +8649,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8634,10 +8663,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8651,7 +8680,7 @@
         <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>85</v>
@@ -8660,16 +8689,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>489</v>
+        <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8695,13 +8724,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>85</v>
+        <v>482</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>85</v>
+        <v>483</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8719,7 +8748,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8734,39 +8763,39 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>493</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>494</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>495</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>499</v>
+        <v>487</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8789,18 +8818,20 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>501</v>
+        <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8824,13 +8855,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8848,7 +8879,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8875,27 +8906,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8906,10 +8937,10 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>85</v>
@@ -8918,20 +8949,18 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -8979,54 +9008,54 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>515</v>
+        <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>85</v>
+        <v>503</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>85</v>
+        <v>504</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>85</v>
+        <v>505</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>85</v>
+        <v>508</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9049,15 +9078,17 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>162</v>
+        <v>510</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>163</v>
+        <v>511</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9106,7 +9137,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>165</v>
+        <v>509</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9118,7 +9149,7 @@
         <v>85</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>85</v>
@@ -9133,31 +9164,31 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>85</v>
+        <v>515</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>166</v>
+        <v>516</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>85</v>
+        <v>517</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9176,18 +9207,20 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>141</v>
+        <v>519</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>142</v>
+        <v>520</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>168</v>
+        <v>521</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
       </c>
@@ -9235,7 +9268,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>172</v>
+        <v>518</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9247,7 +9280,7 @@
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>146</v>
+        <v>524</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9265,10 +9298,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>85</v>
+        <v>525</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>166</v>
+        <v>526</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9279,46 +9312,42 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>521</v>
+        <v>85</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>522</v>
+        <v>163</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9366,19 +9395,19 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>524</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>85</v>
@@ -9399,7 +9428,7 @@
         <v>85</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9410,21 +9439,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -9436,15 +9465,17 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>526</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>527</v>
+        <v>142</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9493,19 +9524,19 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>525</v>
+        <v>172</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>529</v>
+        <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9523,10 +9554,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>531</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9537,42 +9568,46 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>526</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9620,19 +9655,19 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>529</v>
+        <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9650,10 +9685,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>535</v>
+        <v>138</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9664,10 +9699,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9690,20 +9725,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>184</v>
+        <v>535</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>540</v>
-      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9727,13 +9758,13 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>541</v>
+        <v>85</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>542</v>
+        <v>85</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9751,7 +9782,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9760,7 +9791,7 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>107</v>
@@ -9778,13 +9809,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>456</v>
+        <v>540</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9795,10 +9826,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9809,7 +9840,7 @@
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9821,20 +9852,16 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>184</v>
+        <v>535</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
       </c>
@@ -9858,13 +9885,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>472</v>
+        <v>85</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>550</v>
+        <v>85</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>551</v>
+        <v>85</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -9882,16 +9909,16 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
@@ -9909,13 +9936,13 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9926,10 +9953,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9952,17 +9979,19 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>553</v>
+        <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -9987,13 +10016,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>85</v>
+        <v>550</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>85</v>
+        <v>551</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10011,7 +10040,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10038,13 +10067,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>85</v>
+        <v>552</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>85</v>
+        <v>553</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>557</v>
+        <v>465</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10055,10 +10084,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10069,7 +10098,7 @@
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>85</v>
@@ -10081,16 +10110,20 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10114,13 +10147,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>559</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>560</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10138,13 +10171,13 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>85</v>
@@ -10165,13 +10198,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>552</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>530</v>
+        <v>553</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>561</v>
+        <v>465</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10182,10 +10215,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10196,7 +10229,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10205,21 +10238,21 @@
         <v>85</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N62" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10267,13 +10300,13 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>85</v>
@@ -10297,10 +10330,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10311,10 +10344,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10325,7 +10358,7 @@
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>85</v>
@@ -10334,20 +10367,18 @@
         <v>85</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>570</v>
+        <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10396,13 +10427,13 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>85</v>
@@ -10426,10 +10457,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>567</v>
+        <v>539</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10440,10 +10471,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10466,20 +10497,18 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>510</v>
+        <v>572</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10527,7 +10556,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10557,10 +10586,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10571,10 +10600,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10585,7 +10614,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10594,18 +10623,20 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>162</v>
+        <v>579</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>163</v>
+        <v>580</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -10654,19 +10685,19 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>165</v>
+        <v>578</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>85</v>
@@ -10684,10 +10715,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>85</v>
+        <v>576</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>166</v>
+        <v>583</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10698,14 +10729,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10721,21 +10752,23 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>141</v>
+        <v>519</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>142</v>
+        <v>585</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>168</v>
+        <v>586</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
       </c>
@@ -10783,7 +10816,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>172</v>
+        <v>584</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10795,7 +10828,7 @@
         <v>85</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>85</v>
@@ -10813,10 +10846,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>85</v>
+        <v>589</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>166</v>
+        <v>590</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10827,46 +10860,42 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>521</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>522</v>
+        <v>163</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -10914,19 +10943,19 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>524</v>
+        <v>165</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>85</v>
@@ -10947,7 +10976,7 @@
         <v>85</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -10958,21 +10987,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>85</v>
@@ -10981,23 +11010,21 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>586</v>
+        <v>142</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>587</v>
+        <v>168</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11021,13 +11048,13 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>472</v>
+        <v>85</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>589</v>
+        <v>85</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>85</v>
@@ -11045,19 +11072,19 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>585</v>
+        <v>172</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11072,16 +11099,16 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>590</v>
+        <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>285</v>
+        <v>85</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>286</v>
+        <v>166</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>85</v>
@@ -11089,45 +11116,45 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>426</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>592</v>
+        <v>531</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>593</v>
+        <v>532</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>594</v>
+        <v>144</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>430</v>
+        <v>150</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11176,19 +11203,19 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>591</v>
+        <v>533</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11203,27 +11230,27 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>595</v>
+        <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>434</v>
+        <v>85</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>435</v>
+        <v>138</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11231,7 +11258,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>95</v>
@@ -11243,22 +11270,22 @@
         <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>599</v>
-      </c>
       <c r="O70" t="s" s="2">
-        <v>441</v>
+        <v>280</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11283,13 +11310,13 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>189</v>
+        <v>481</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>442</v>
+        <v>282</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11307,16 +11334,16 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>107</v>
@@ -11334,16 +11361,16 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>85</v>
+        <v>599</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>138</v>
+        <v>285</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>445</v>
+        <v>286</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>85</v>
@@ -11351,21 +11378,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11374,22 +11401,22 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>184</v>
+        <v>435</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>448</v>
+        <v>601</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>449</v>
+        <v>602</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>450</v>
+        <v>603</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11414,13 +11441,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>453</v>
+        <v>85</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11438,13 +11465,13 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
@@ -11465,27 +11492,27 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>454</v>
+        <v>604</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>457</v>
+        <v>445</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11496,7 +11523,7 @@
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
@@ -11508,19 +11535,19 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>513</v>
+        <v>608</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>514</v>
+        <v>450</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11545,13 +11572,13 @@
         <v>85</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>85</v>
+        <v>609</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>85</v>
+        <v>451</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11569,16 +11596,16 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>85</v>
+        <v>610</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>107</v>
@@ -11599,20 +11626,282 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>516</v>
+        <v>138</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>517</v>
+        <v>454</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS73" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS74" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS72">
+  <autoFilter ref="A1:AS74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11622,7 +11911,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1320,6 +1320,10 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1407,6 +1411,37 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>2109: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>2110: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>2111: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2255,12 +2290,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS74"/>
+  <dimension ref="A1:AS77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -7825,7 +7860,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>269</v>
+        <v>418</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7859,19 +7894,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7879,13 +7914,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -7907,7 +7942,7 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>415</v>
@@ -7981,28 +8016,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8010,13 +8045,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8038,7 +8073,7 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>415</v>
@@ -8112,28 +8147,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8141,10 +8176,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8167,19 +8202,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8216,19 +8251,17 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8237,10 +8270,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8255,29 +8288,31 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
       </c>
@@ -8295,22 +8330,22 @@
         <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>184</v>
+        <v>449</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8335,11 +8370,13 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>451</v>
+        <v>85</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8357,7 +8394,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8366,13 +8403,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>107</v>
+        <v>442</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8384,62 +8421,64 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>138</v>
+        <v>444</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>85</v>
+        <v>446</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>456</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8464,13 +8503,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>462</v>
+        <v>85</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8488,22 +8527,22 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>107</v>
+        <v>442</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8515,29 +8554,31 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>466</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>85</v>
       </c>
@@ -8546,7 +8587,7 @@
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>96</v>
@@ -8555,22 +8596,22 @@
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>468</v>
+        <v>162</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8619,25 +8660,25 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>107</v>
+        <v>442</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>474</v>
+        <v>85</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8646,27 +8687,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>85</v>
+        <v>446</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8680,7 +8721,7 @@
         <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>85</v>
@@ -8692,15 +8733,17 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
       </c>
@@ -8724,13 +8767,11 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8748,7 +8789,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8757,13 +8798,13 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>85</v>
+        <v>463</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>85</v>
+        <v>464</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8775,38 +8816,38 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>485</v>
+        <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>487</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -8821,16 +8862,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8855,13 +8896,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>481</v>
+        <v>189</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8879,13 +8920,13 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -8906,27 +8947,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>85</v>
+        <v>474</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>85</v>
+        <v>477</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8937,7 +8978,7 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>96</v>
@@ -8949,18 +8990,20 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -9008,13 +9051,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -9023,39 +9066,39 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>504</v>
+        <v>85</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9078,16 +9121,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>510</v>
+        <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9113,13 +9156,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9137,7 +9180,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9164,27 +9207,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>517</v>
+        <v>498</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9195,7 +9238,7 @@
         <v>83</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>85</v>
@@ -9207,19 +9250,19 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>519</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9244,13 +9287,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>85</v>
+        <v>504</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>85</v>
+        <v>505</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9268,19 +9311,19 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>524</v>
+        <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9298,10 +9341,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9312,10 +9355,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9329,7 +9372,7 @@
         <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>85</v>
@@ -9338,15 +9381,17 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>162</v>
+        <v>509</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9395,7 +9440,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>165</v>
+        <v>508</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9407,53 +9452,53 @@
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>85</v>
+        <v>513</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>85</v>
+        <v>515</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>85</v>
+        <v>516</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>85</v>
+        <v>517</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>166</v>
+        <v>518</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>85</v>
+        <v>519</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -9465,16 +9510,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>141</v>
+        <v>521</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>142</v>
+        <v>522</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>168</v>
+        <v>523</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>144</v>
+        <v>524</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9524,19 +9569,19 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>172</v>
+        <v>520</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9551,19 +9596,19 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>85</v>
+        <v>525</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>85</v>
+        <v>526</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>166</v>
+        <v>527</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>85</v>
+        <v>528</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9575,7 +9620,7 @@
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9588,13 +9633,13 @@
         <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>141</v>
+        <v>530</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>531</v>
@@ -9603,10 +9648,10 @@
         <v>532</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>144</v>
+        <v>533</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>150</v>
+        <v>534</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9655,7 +9700,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9667,7 +9712,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>146</v>
+        <v>535</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9685,10 +9730,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>85</v>
+        <v>536</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>138</v>
+        <v>537</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9699,10 +9744,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9725,13 +9770,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>535</v>
+        <v>162</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>536</v>
+        <v>163</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>537</v>
+        <v>164</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9782,7 +9827,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>534</v>
+        <v>165</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9791,10 +9836,10 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>538</v>
+        <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9812,10 +9857,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>539</v>
+        <v>85</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>540</v>
+        <v>166</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9826,21 +9871,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9852,15 +9897,17 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>535</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>542</v>
+        <v>142</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9909,19 +9956,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>541</v>
+        <v>172</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>538</v>
+        <v>85</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -9939,10 +9986,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>539</v>
+        <v>85</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>544</v>
+        <v>166</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9953,45 +10000,45 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>85</v>
+        <v>541</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>548</v>
+        <v>144</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>549</v>
+        <v>150</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10016,13 +10063,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>550</v>
+        <v>85</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>551</v>
+        <v>85</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10040,19 +10087,19 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10067,13 +10114,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>552</v>
+        <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>553</v>
+        <v>85</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>465</v>
+        <v>138</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10084,10 +10131,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10098,7 +10145,7 @@
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>85</v>
@@ -10110,20 +10157,16 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>184</v>
+        <v>546</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10147,13 +10190,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>559</v>
+        <v>85</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>560</v>
+        <v>85</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10171,16 +10214,16 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10198,13 +10241,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>552</v>
+        <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>465</v>
+        <v>551</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10215,10 +10258,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10241,18 +10284,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>565</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10300,7 +10341,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10309,7 +10350,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10330,10 +10371,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>85</v>
+        <v>550</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10344,10 +10385,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10370,16 +10411,20 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
@@ -10403,13 +10448,13 @@
         <v>85</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>85</v>
+        <v>561</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>85</v>
+        <v>562</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10427,7 +10472,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10454,13 +10499,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>85</v>
+        <v>563</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>570</v>
+        <v>476</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10471,10 +10516,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10494,21 +10539,23 @@
         <v>85</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>572</v>
+        <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10532,13 +10579,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>85</v>
+        <v>570</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>85</v>
+        <v>571</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10556,7 +10603,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10583,13 +10630,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>85</v>
+        <v>563</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>577</v>
+        <v>476</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10600,10 +10647,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10614,7 +10661,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10623,21 +10670,21 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10685,13 +10732,13 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
@@ -10715,10 +10762,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>576</v>
+        <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10729,10 +10776,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10743,7 +10790,7 @@
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10752,23 +10799,19 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>519</v>
+        <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>588</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
       </c>
@@ -10816,13 +10859,13 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
@@ -10846,10 +10889,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10860,10 +10903,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10874,7 +10917,7 @@
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>85</v>
@@ -10883,18 +10926,20 @@
         <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>162</v>
+        <v>583</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>163</v>
+        <v>584</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
@@ -10943,19 +10988,19 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>165</v>
+        <v>582</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>85</v>
@@ -10973,10 +11018,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>166</v>
+        <v>588</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -10987,14 +11032,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -11010,19 +11055,19 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>141</v>
+        <v>590</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>142</v>
+        <v>591</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>168</v>
+        <v>592</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>144</v>
+        <v>593</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11072,7 +11117,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>172</v>
+        <v>589</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11084,7 +11129,7 @@
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11102,10 +11147,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>166</v>
+        <v>594</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11116,14 +11161,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11136,25 +11181,25 @@
         <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>141</v>
+        <v>530</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>531</v>
+        <v>596</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>532</v>
+        <v>597</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>144</v>
+        <v>598</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>150</v>
+        <v>599</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11203,7 +11248,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>533</v>
+        <v>595</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11215,7 +11260,7 @@
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11233,10 +11278,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>138</v>
+        <v>601</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11247,10 +11292,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11258,7 +11303,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>95</v>
@@ -11270,23 +11315,19 @@
         <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>595</v>
+        <v>163</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11310,13 +11351,13 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>598</v>
+        <v>85</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11334,10 +11375,10 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>594</v>
+        <v>165</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>95</v>
@@ -11346,7 +11387,7 @@
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11361,16 +11402,16 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>599</v>
+        <v>85</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>285</v>
+        <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>286</v>
+        <v>166</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>85</v>
@@ -11378,21 +11419,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11401,23 +11442,21 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>435</v>
+        <v>141</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>601</v>
+        <v>142</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>602</v>
+        <v>168</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11465,19 +11504,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>600</v>
+        <v>172</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11492,62 +11531,62 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>604</v>
+        <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>443</v>
+        <v>85</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>444</v>
+        <v>166</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>85</v>
+        <v>541</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>606</v>
+        <v>542</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>607</v>
+        <v>543</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>608</v>
+        <v>144</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11572,13 +11611,13 @@
         <v>85</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>609</v>
+        <v>85</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>451</v>
+        <v>85</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11596,19 +11635,19 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>605</v>
+        <v>544</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>610</v>
+        <v>85</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>85</v>
@@ -11626,10 +11665,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11640,21 +11679,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>456</v>
+        <v>85</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -11663,22 +11702,22 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>457</v>
+        <v>606</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>458</v>
+        <v>607</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>459</v>
+        <v>608</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>460</v>
+        <v>280</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11703,13 +11742,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>189</v>
+        <v>492</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>461</v>
+        <v>609</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>462</v>
+        <v>282</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11727,13 +11766,13 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>85</v>
@@ -11754,27 +11793,27 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>463</v>
+        <v>610</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>464</v>
+        <v>285</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>465</v>
+        <v>286</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="AS73" t="s" s="2">
-        <v>466</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11785,7 +11824,7 @@
         <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>85</v>
@@ -11794,22 +11833,22 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>86</v>
+        <v>436</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="N74" t="s" s="2">
-        <v>522</v>
-      </c>
       <c r="O74" t="s" s="2">
-        <v>523</v>
+        <v>440</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11858,13 +11897,13 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>85</v>
@@ -11885,23 +11924,416 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>525</v>
+        <v>444</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>526</v>
+        <v>445</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS75" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS76" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS77" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS74">
+  <autoFilter ref="A1:AS77">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11911,7 +12343,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI73">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="624">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -671,7 +671,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1476: source value from MICROBIOLOGY - IEN (63.05-.001)</t>
+    <t>1476: source value based on MICROBIOLOGY - IEN (63.05-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -900,6 +900,13 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lommo-45-1527:If (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) is NULL then fixed value http://loinc.org#42804-5 "Fungus identified in Isolate" {null}</t>
+  </si>
+  <si>
+    <t>1527: fixed value = http://loinc.org#42804-5 "Fungus identified in Isolate" when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if NULL</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -946,7 +953,11 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lommo-45-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {null}</t>
+  </si>
+  <si>
+    <t>1480: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if Not NULL</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -980,10 +991,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lommo-45-1480-1:undefined: if Not NULL then http://loinc.org {null}</t>
-  </si>
-  <si>
-    <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
+lommo-45-1480-1:If (undefined) is Not NULL then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
+    <t>1480-1: fixed value = http://loinc.org if Not NULL</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -1028,7 +1039,11 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1480-2: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lommo-45-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {null}</t>
+  </si>
+  <si>
+    <t>1480-2: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) if Not NULL</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1052,7 +1067,11 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1480-3: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lommo-45-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {null}</t>
+  </si>
+  <si>
+    <t>1480-3: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) if Not NULL</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1132,7 +1151,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>844: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1264,7 +1283,7 @@
 </t>
   </si>
   <si>
-    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
+    <t>1450: source value based on MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
@@ -1286,7 +1305,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
+    <t>1484: source value based on MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1346,7 +1365,7 @@
 </t>
   </si>
   <si>
-    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+    <t>1464: reference based on MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
@@ -1365,7 +1384,7 @@
 </t>
   </si>
   <si>
-    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+    <t>1679: reference based on MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
@@ -1413,35 +1432,13 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>2109: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>2110: target not supported</t>
-  </si>
-  <si>
     <t>Observation.value[x]:valueString</t>
   </si>
   <si>
     <t>valueString</t>
   </si>
   <si>
-    <t>2111: target not supported</t>
+    <t>1858: source value based on MICROBIOLOGY - FUNGUS/YEAST &gt; FUNGUS/YEAST - FUNGUS/YEAST &gt; ETIOLOGY FIELD - NAME (63.05-20 &gt; 63.37-.01 &gt; 61.2-.01)</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1529,7 +1526,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1454: source value from MICROBIOLOGY - COMMENT ON SPECIMEN (63.05-.99)</t>
+    <t>1454: source value based on MICROBIOLOGY - COMMENT ON SPECIMEN (63.05-.99)</t>
   </si>
   <si>
     <t>Micro.Microbiology.SpecimenComment</t>
@@ -1618,7 +1615,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
+    <t>1659: reference based on MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
@@ -2290,12 +2287,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS77"/>
+  <dimension ref="A1:AS75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2328,7 +2325,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -5550,10 +5547,10 @@
         <v>85</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>85</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>85</v>
@@ -5562,30 +5559,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5709,10 +5706,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5838,10 +5835,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5864,19 +5861,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -5925,7 +5922,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5937,10 +5934,10 @@
         <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -5955,10 +5952,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -5969,10 +5966,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6096,10 +6093,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6225,10 +6222,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6254,16 +6251,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6312,7 +6309,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6324,10 +6321,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6342,10 +6339,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6356,10 +6353,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6385,13 +6382,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6441,7 +6438,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6471,10 +6468,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6485,10 +6482,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6514,14 +6511,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6570,7 +6567,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6582,10 +6579,10 @@
         <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6600,10 +6597,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6614,10 +6611,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6643,14 +6640,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6699,7 +6696,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6711,10 +6708,10 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>107</v>
+        <v>337</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6729,10 +6726,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6743,10 +6740,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6769,19 +6766,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6830,7 +6827,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6860,10 +6857,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6874,10 +6871,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6903,16 +6900,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6961,7 +6958,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6991,10 +6988,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -7005,10 +7002,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7031,19 +7028,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7092,7 +7089,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7107,28 +7104,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7136,10 +7133,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7162,16 +7159,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7221,7 +7218,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7251,13 +7248,13 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7265,14 +7262,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7291,19 +7288,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7352,7 +7349,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7376,19 +7373,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7396,14 +7393,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7422,19 +7419,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7471,7 +7468,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7481,7 +7478,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7490,10 +7487,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7505,19 +7502,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7525,16 +7522,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7553,19 +7550,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7614,7 +7611,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7623,34 +7620,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AR41" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7658,10 +7655,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7684,16 +7681,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7743,7 +7740,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7758,13 +7755,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7773,13 +7770,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7787,10 +7784,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7813,17 +7810,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7860,7 +7857,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7870,7 +7867,7 @@
         <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7894,19 +7891,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7914,13 +7911,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -7942,17 +7939,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8001,7 +7998,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8016,28 +8013,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AR44" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8045,13 +8042,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8073,17 +8070,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8132,7 +8129,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8147,28 +8144,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8176,10 +8173,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8202,19 +8199,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8251,7 +8248,7 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8261,7 +8258,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8270,10 +8267,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8288,30 +8285,30 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8333,19 +8330,19 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>449</v>
+        <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8394,7 +8391,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8403,49 +8400,47 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8463,22 +8458,22 @@
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8503,13 +8498,11 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8527,7 +8520,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8536,13 +8529,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>442</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8554,64 +8547,62 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>443</v>
+        <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>444</v>
+        <v>138</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>446</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>85</v>
+        <v>465</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8636,13 +8627,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>85</v>
+        <v>471</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8660,22 +8651,22 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>441</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>442</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>456</v>
+        <v>85</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>85</v>
@@ -8687,27 +8678,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>446</v>
+        <v>475</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8718,7 +8709,7 @@
         <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>96</v>
@@ -8730,19 +8721,19 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>184</v>
+        <v>477</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8767,11 +8758,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>462</v>
+        <v>85</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8789,25 +8782,25 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>463</v>
+        <v>85</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>85</v>
+        <v>483</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>85</v>
@@ -8819,10 +8812,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>138</v>
+        <v>484</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8833,21 +8826,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>467</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -8862,17 +8855,15 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8896,13 +8887,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>189</v>
+        <v>490</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8920,13 +8911,13 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -8947,27 +8938,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>477</v>
+        <v>496</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8978,10 +8969,10 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>85</v>
@@ -8990,19 +8981,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>479</v>
+        <v>184</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9027,13 +9018,13 @@
         <v>85</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>85</v>
+        <v>503</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>85</v>
@@ -9051,13 +9042,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -9066,10 +9057,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>485</v>
+        <v>85</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>85</v>
@@ -9081,10 +9072,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9095,10 +9086,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9112,7 +9103,7 @@
         <v>95</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>85</v>
@@ -9121,16 +9112,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>507</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9156,13 +9147,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>493</v>
+        <v>85</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>494</v>
+        <v>85</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9180,7 +9171,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9195,39 +9186,39 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>85</v>
+        <v>511</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>85</v>
+        <v>512</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>85</v>
+        <v>513</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>498</v>
+        <v>517</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9250,20 +9241,18 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>184</v>
+        <v>519</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>85</v>
       </c>
@@ -9287,13 +9276,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>504</v>
+        <v>85</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9311,7 +9300,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9338,27 +9327,27 @@
         <v>85</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>85</v>
+        <v>523</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>85</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9369,10 +9358,10 @@
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>85</v>
@@ -9381,18 +9370,20 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9440,54 +9431,54 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>107</v>
+        <v>533</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>513</v>
+        <v>85</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>514</v>
+        <v>85</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>515</v>
+        <v>85</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>516</v>
+        <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>519</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9510,17 +9501,15 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>521</v>
+        <v>162</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>522</v>
+        <v>163</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9569,7 +9558,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>520</v>
+        <v>165</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9581,7 +9570,7 @@
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9596,31 +9585,31 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>525</v>
+        <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>527</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>528</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9639,20 +9628,18 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>530</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>531</v>
+        <v>142</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>532</v>
+        <v>168</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9700,7 +9687,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>529</v>
+        <v>172</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9712,7 +9699,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>535</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9730,10 +9717,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>536</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>537</v>
+        <v>166</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9751,35 +9738,39 @@
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>85</v>
+        <v>539</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>163</v>
+        <v>540</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9827,19 +9818,19 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>165</v>
+        <v>542</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9860,7 +9851,7 @@
         <v>85</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9871,21 +9862,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9897,17 +9888,15 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>141</v>
+        <v>544</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>142</v>
+        <v>545</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9956,19 +9945,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>172</v>
+        <v>543</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>547</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -9986,10 +9975,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>85</v>
+        <v>548</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>166</v>
+        <v>549</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10000,46 +9989,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>541</v>
+        <v>85</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>141</v>
+        <v>544</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>85</v>
       </c>
@@ -10087,19 +10072,19 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>85</v>
+        <v>547</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10117,10 +10102,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>85</v>
+        <v>548</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>138</v>
+        <v>553</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10131,10 +10116,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10157,16 +10142,20 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>546</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10190,13 +10179,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>559</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>560</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10214,7 +10203,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10223,7 +10212,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>549</v>
+        <v>85</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10241,13 +10230,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>561</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>551</v>
+        <v>474</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10258,10 +10247,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10272,7 +10261,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10284,16 +10273,20 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>546</v>
+        <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10317,13 +10310,13 @@
         <v>85</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>85</v>
+        <v>568</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>85</v>
+        <v>569</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10341,16 +10334,16 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>549</v>
+        <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10368,13 +10361,13 @@
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>85</v>
+        <v>561</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>555</v>
+        <v>474</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10385,10 +10378,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10411,19 +10404,17 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>184</v>
+        <v>571</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10448,13 +10439,13 @@
         <v>85</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>561</v>
+        <v>85</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>562</v>
+        <v>85</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10472,7 +10463,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10499,13 +10490,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>563</v>
+        <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>564</v>
+        <v>85</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>476</v>
+        <v>575</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10516,10 +10507,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10530,7 +10521,7 @@
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>85</v>
@@ -10542,20 +10533,16 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>569</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10579,13 +10566,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>570</v>
+        <v>85</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>571</v>
+        <v>85</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10603,13 +10590,13 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>85</v>
@@ -10630,13 +10617,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>563</v>
+        <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>476</v>
+        <v>579</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10647,10 +10634,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10661,7 +10648,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10670,21 +10657,21 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10732,13 +10719,13 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
@@ -10762,10 +10749,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>85</v>
+        <v>585</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10776,10 +10763,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10790,7 +10777,7 @@
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10799,18 +10786,20 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>162</v>
+        <v>588</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10859,13 +10848,13 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
@@ -10889,10 +10878,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>550</v>
+        <v>585</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10903,10 +10892,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10929,18 +10918,20 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>583</v>
+        <v>528</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -10988,7 +10979,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11018,10 +11009,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11032,10 +11023,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11046,7 +11037,7 @@
         <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>85</v>
@@ -11055,20 +11046,18 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>590</v>
+        <v>162</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>591</v>
+        <v>163</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11117,19 +11106,19 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>589</v>
+        <v>165</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11147,10 +11136,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>594</v>
+        <v>166</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11161,14 +11150,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11184,23 +11173,21 @@
         <v>85</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>530</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>596</v>
+        <v>142</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>597</v>
+        <v>168</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11248,7 +11235,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>595</v>
+        <v>172</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11260,7 +11247,7 @@
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11278,10 +11265,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>601</v>
+        <v>166</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11299,35 +11286,39 @@
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>85</v>
+        <v>539</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>163</v>
+        <v>540</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11375,19 +11366,19 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>165</v>
+        <v>542</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11408,7 +11399,7 @@
         <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11426,14 +11417,14 @@
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11442,21 +11433,23 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>142</v>
+        <v>604</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>168</v>
+        <v>605</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>606</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11480,13 +11473,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>85</v>
+        <v>607</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11504,19 +11497,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>172</v>
+        <v>603</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11531,16 +11524,16 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>85</v>
+        <v>608</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>166</v>
+        <v>288</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>85</v>
+        <v>289</v>
       </c>
       <c r="AS71" t="s" s="2">
         <v>85</v>
@@ -11548,45 +11541,45 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>541</v>
+        <v>85</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>141</v>
+        <v>441</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>542</v>
+        <v>610</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>543</v>
+        <v>611</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>144</v>
+        <v>612</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>150</v>
+        <v>445</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11635,19 +11628,19 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>544</v>
+        <v>609</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>85</v>
@@ -11662,27 +11655,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>85</v>
+        <v>613</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>85</v>
+        <v>449</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>138</v>
+        <v>450</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>85</v>
+        <v>451</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11690,7 +11683,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>95</v>
@@ -11702,22 +11695,22 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>280</v>
+        <v>459</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11742,13 +11735,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>492</v>
+        <v>189</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>282</v>
+        <v>460</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11766,16 +11759,16 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>85</v>
+        <v>619</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>107</v>
@@ -11793,16 +11786,16 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>610</v>
+        <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>285</v>
+        <v>138</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>286</v>
+        <v>463</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>85</v>
@@ -11810,21 +11803,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>85</v>
+        <v>465</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>85</v>
@@ -11833,22 +11826,22 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>436</v>
+        <v>184</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>612</v>
+        <v>466</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>613</v>
+        <v>467</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>614</v>
+        <v>468</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11873,13 +11866,13 @@
         <v>85</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>85</v>
+        <v>471</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>85</v>
@@ -11897,13 +11890,13 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>85</v>
@@ -11924,27 +11917,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>615</v>
+        <v>472</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>446</v>
+        <v>475</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11955,7 +11948,7 @@
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
@@ -11967,19 +11960,19 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>619</v>
+        <v>531</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>461</v>
+        <v>532</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12004,13 +11997,13 @@
         <v>85</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>620</v>
+        <v>85</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>462</v>
+        <v>85</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12028,16 +12021,16 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>621</v>
+        <v>85</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12058,282 +12051,20 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>138</v>
+        <v>534</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>465</v>
+        <v>535</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS75" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS76" t="s" s="2">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS77" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS77">
+  <autoFilter ref="A1:AS75">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12343,7 +12074,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="630">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -798,6 +798,9 @@
   </si>
   <si>
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_LabObservationStatus](ConceptMap-VF-LabObservationStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/LabObservationStatus</t>
@@ -900,13 +903,6 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lommo-45-1527:If (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) is NULL then fixed value http://loinc.org#42804-5 "Fungus identified in Isolate" {null}</t>
-  </si>
-  <si>
-    <t>1527: fixed value = http://loinc.org#42804-5 "Fungus identified in Isolate" when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if NULL</t>
-  </si>
-  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -1432,13 +1428,35 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>2109: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>2110: target not supported</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueString</t>
   </si>
   <si>
     <t>valueString</t>
   </si>
   <si>
-    <t>1858: source value based on MICROBIOLOGY - FUNGUS/YEAST &gt; FUNGUS/YEAST - FUNGUS/YEAST &gt; ETIOLOGY FIELD - NAME (63.05-20 &gt; 63.37-.01 &gt; 61.2-.01)</t>
+    <t>2111: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2287,12 +2305,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS75"/>
+  <dimension ref="A1:AS77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2325,7 +2343,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="251.96875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -5122,9 +5140,11 @@
       <c r="X22" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>85</v>
@@ -5157,28 +5177,28 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -5186,10 +5206,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5215,16 +5235,16 @@
         <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>85</v>
@@ -5234,7 +5254,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5252,16 +5272,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5271,7 +5291,7 @@
         <v>171</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5286,7 +5306,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>85</v>
@@ -5304,10 +5324,10 @@
         <v>85</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5315,13 +5335,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5346,16 +5366,16 @@
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5365,7 +5385,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5383,10 +5403,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5404,7 +5424,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5437,10 +5457,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -5448,14 +5468,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5477,16 +5497,16 @@
         <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5514,10 +5534,10 @@
         <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -5535,7 +5555,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>95</v>
@@ -5547,42 +5567,42 @@
         <v>85</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AQ25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AR25" t="s" s="2">
+      <c r="AS25" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AS25" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5706,10 +5726,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5835,10 +5855,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5861,19 +5881,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -5922,7 +5942,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5934,28 +5954,28 @@
         <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -5966,10 +5986,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6093,10 +6113,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6222,10 +6242,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6251,16 +6271,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6309,7 +6329,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6321,28 +6341,28 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6353,10 +6373,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6382,13 +6402,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6438,7 +6458,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6468,10 +6488,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6482,10 +6502,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6511,14 +6531,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6567,7 +6587,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6579,28 +6599,28 @@
         <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AK33" t="s" s="2">
+      <c r="AL33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6611,10 +6631,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6640,14 +6660,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6696,7 +6716,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6708,28 +6728,28 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK34" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AK34" t="s" s="2">
+      <c r="AL34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6740,10 +6760,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6766,19 +6786,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6827,7 +6847,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6857,10 +6877,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6871,10 +6891,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6900,16 +6920,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6958,7 +6978,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6988,10 +7008,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -7002,10 +7022,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7028,19 +7048,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7089,7 +7109,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7104,28 +7124,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AQ37" t="s" s="2">
+      <c r="AR37" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7133,10 +7153,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7159,16 +7179,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7218,7 +7238,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7248,13 +7268,13 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7262,14 +7282,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7288,19 +7308,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7349,7 +7369,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7373,19 +7393,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AO39" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AQ39" t="s" s="2">
+      <c r="AR39" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7393,14 +7413,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7419,19 +7439,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7468,7 +7488,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7478,7 +7498,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7487,34 +7507,34 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AJ40" t="s" s="2">
+      <c r="AK40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AK40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AQ40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7522,16 +7542,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="B41" t="s" s="2">
+      <c r="D41" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7550,19 +7570,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7611,7 +7631,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7620,34 +7640,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AJ41" t="s" s="2">
+      <c r="AK41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AK41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AQ41" t="s" s="2">
+      <c r="AR41" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7655,10 +7675,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7681,16 +7701,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7740,7 +7760,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7755,28 +7775,28 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AN42" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AQ42" t="s" s="2">
+      <c r="AR42" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AR42" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7784,10 +7804,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7810,17 +7830,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7857,7 +7877,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7867,7 +7887,7 @@
         <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7891,19 +7911,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AO43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AQ43" t="s" s="2">
+      <c r="AR43" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7911,13 +7931,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C44" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -7939,17 +7959,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7998,7 +8018,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8013,28 +8033,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="AN44" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AQ44" t="s" s="2">
+      <c r="AR44" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8042,13 +8062,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8070,17 +8090,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8129,7 +8149,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8144,28 +8164,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AN45" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AO45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AQ45" t="s" s="2">
+      <c r="AR45" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8173,10 +8193,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8199,19 +8219,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8248,7 +8268,7 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8258,7 +8278,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8267,48 +8287,48 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AJ46" t="s" s="2">
+      <c r="AK46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AK46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AQ46" t="s" s="2">
+      <c r="AR46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS46" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8330,19 +8350,19 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>162</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8391,7 +8411,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8400,10 +8420,10 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>454</v>
@@ -8418,19 +8438,19 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AQ47" t="s" s="2">
+      <c r="AR47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS47" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8438,9 +8458,11 @@
         <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8458,22 +8480,22 @@
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8498,11 +8520,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8520,7 +8544,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8529,13 +8553,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>107</v>
+        <v>446</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8547,62 +8571,64 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>85</v>
+        <v>447</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>138</v>
+        <v>448</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>85</v>
+        <v>450</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8627,13 +8653,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>470</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>471</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8651,22 +8677,22 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>85</v>
+        <v>445</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>107</v>
+        <v>446</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>85</v>
@@ -8678,27 +8704,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>475</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8709,7 +8735,7 @@
         <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>96</v>
@@ -8721,19 +8747,19 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>477</v>
+        <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8758,13 +8784,11 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8782,25 +8806,25 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>483</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>85</v>
@@ -8812,10 +8836,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>484</v>
+        <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8826,21 +8850,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>85</v>
+        <v>471</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -8855,15 +8879,17 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8887,13 +8913,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>490</v>
+        <v>189</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8911,13 +8937,13 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -8938,27 +8964,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>496</v>
+        <v>481</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8969,10 +8995,10 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>85</v>
@@ -8981,19 +9007,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>184</v>
+        <v>483</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9018,13 +9044,13 @@
         <v>85</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>502</v>
+        <v>85</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>503</v>
+        <v>85</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>85</v>
@@ -9042,13 +9068,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -9057,10 +9083,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>488</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>85</v>
+        <v>489</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>85</v>
@@ -9072,10 +9098,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9086,10 +9112,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9103,7 +9129,7 @@
         <v>95</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>85</v>
@@ -9112,16 +9138,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>507</v>
+        <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9147,13 +9173,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>85</v>
+        <v>496</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>85</v>
+        <v>497</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>85</v>
+        <v>498</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9171,7 +9197,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9186,39 +9212,39 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>512</v>
+        <v>85</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>513</v>
+        <v>85</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>517</v>
+        <v>502</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9241,18 +9267,20 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>519</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
       </c>
@@ -9276,13 +9304,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>85</v>
+        <v>496</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>85</v>
+        <v>508</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>85</v>
+        <v>509</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9300,7 +9328,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9327,27 +9355,27 @@
         <v>85</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>523</v>
+        <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9358,10 +9386,10 @@
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>85</v>
@@ -9370,20 +9398,18 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9431,54 +9457,54 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>533</v>
+        <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>85</v>
+        <v>517</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>85</v>
+        <v>518</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>85</v>
+        <v>519</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>85</v>
+        <v>520</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>85</v>
+        <v>523</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9501,15 +9527,17 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>162</v>
+        <v>525</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>163</v>
+        <v>526</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9558,7 +9586,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>165</v>
+        <v>524</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9570,7 +9598,7 @@
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9585,31 +9613,31 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>85</v>
+        <v>529</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>166</v>
+        <v>531</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>85</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9628,18 +9656,20 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>141</v>
+        <v>534</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>142</v>
+        <v>535</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>168</v>
+        <v>536</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9687,7 +9717,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>172</v>
+        <v>533</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9699,7 +9729,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>146</v>
+        <v>539</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9717,10 +9747,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>85</v>
+        <v>540</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>166</v>
+        <v>541</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9731,46 +9761,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>539</v>
+        <v>85</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>540</v>
+        <v>163</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9818,19 +9844,19 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>542</v>
+        <v>165</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9851,7 +9877,7 @@
         <v>85</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9869,14 +9895,14 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9888,15 +9914,17 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>544</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>545</v>
+        <v>142</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9945,19 +9973,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>543</v>
+        <v>172</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -9975,10 +10003,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>548</v>
+        <v>85</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>549</v>
+        <v>166</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9989,42 +10017,46 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>85</v>
+        <v>545</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>544</v>
+        <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
       </c>
@@ -10072,19 +10104,19 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10102,10 +10134,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>548</v>
+        <v>85</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>553</v>
+        <v>138</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10116,10 +10148,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10142,20 +10174,16 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>184</v>
+        <v>550</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10179,13 +10207,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>559</v>
+        <v>85</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>560</v>
+        <v>85</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10203,7 +10231,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10212,7 +10240,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>85</v>
+        <v>553</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10230,13 +10258,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>561</v>
+        <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>474</v>
+        <v>555</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10247,10 +10275,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10261,7 +10289,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10273,20 +10301,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>184</v>
+        <v>550</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10310,13 +10334,13 @@
         <v>85</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>568</v>
+        <v>85</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>569</v>
+        <v>85</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10334,16 +10358,16 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>85</v>
+        <v>553</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10361,13 +10385,13 @@
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>561</v>
+        <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>474</v>
+        <v>559</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10378,10 +10402,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10404,17 +10428,19 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>571</v>
+        <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>562</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10439,13 +10465,13 @@
         <v>85</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>85</v>
+        <v>566</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10463,7 +10489,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10490,13 +10516,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>85</v>
+        <v>568</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>575</v>
+        <v>480</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10507,10 +10533,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10521,7 +10547,7 @@
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>85</v>
@@ -10533,16 +10559,20 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10566,13 +10596,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>85</v>
+        <v>496</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>85</v>
+        <v>574</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>85</v>
+        <v>575</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10590,13 +10620,13 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>85</v>
@@ -10617,13 +10647,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>579</v>
+        <v>480</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10634,10 +10664,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10648,7 +10678,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10657,21 +10687,21 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10719,13 +10749,13 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
@@ -10749,10 +10779,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>585</v>
+        <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10763,10 +10793,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10777,7 +10807,7 @@
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10786,20 +10816,18 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>588</v>
+        <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10848,13 +10876,13 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
@@ -10878,10 +10906,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10892,10 +10920,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10918,20 +10946,18 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -10979,7 +11005,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11009,10 +11035,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11023,10 +11049,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11037,7 +11063,7 @@
         <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>85</v>
@@ -11046,18 +11072,20 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>162</v>
+        <v>594</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>163</v>
+        <v>595</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11106,19 +11134,19 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>165</v>
+        <v>593</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11136,10 +11164,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>85</v>
+        <v>591</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>166</v>
+        <v>598</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11150,14 +11178,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11173,21 +11201,23 @@
         <v>85</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>141</v>
+        <v>534</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>142</v>
+        <v>600</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>168</v>
+        <v>601</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11235,7 +11265,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>172</v>
+        <v>599</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11247,7 +11277,7 @@
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11265,10 +11295,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>166</v>
+        <v>605</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11279,46 +11309,42 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>539</v>
+        <v>85</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>540</v>
+        <v>163</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11366,19 +11392,19 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>542</v>
+        <v>165</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11399,7 +11425,7 @@
         <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11410,21 +11436,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11433,23 +11459,21 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>604</v>
+        <v>142</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>605</v>
+        <v>168</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11473,13 +11497,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>607</v>
+        <v>85</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11497,19 +11521,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>603</v>
+        <v>172</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11524,16 +11548,16 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>608</v>
+        <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>288</v>
+        <v>166</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>289</v>
+        <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
         <v>85</v>
@@ -11541,45 +11565,45 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>85</v>
+        <v>545</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>441</v>
+        <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>610</v>
+        <v>546</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>611</v>
+        <v>547</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>612</v>
+        <v>144</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>445</v>
+        <v>150</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11628,19 +11652,19 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>609</v>
+        <v>548</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>85</v>
@@ -11655,27 +11679,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>613</v>
+        <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>449</v>
+        <v>85</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>450</v>
+        <v>138</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>451</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11683,7 +11707,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>95</v>
@@ -11695,22 +11719,22 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>459</v>
+        <v>281</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11735,13 +11759,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>189</v>
+        <v>496</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>460</v>
+        <v>283</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11759,16 +11783,16 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>619</v>
+        <v>85</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>107</v>
@@ -11786,16 +11810,16 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>85</v>
+        <v>614</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>463</v>
+        <v>287</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>85</v>
+        <v>288</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>85</v>
@@ -11803,21 +11827,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>85</v>
@@ -11826,22 +11850,22 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>184</v>
+        <v>440</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>466</v>
+        <v>616</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>467</v>
+        <v>617</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>468</v>
+        <v>618</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11866,13 +11890,13 @@
         <v>85</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>470</v>
+        <v>85</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>471</v>
+        <v>85</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>85</v>
@@ -11890,13 +11914,13 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>85</v>
@@ -11917,27 +11941,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>472</v>
+        <v>619</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>475</v>
+        <v>450</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11948,7 +11972,7 @@
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
@@ -11960,19 +11984,19 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N75" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>532</v>
+        <v>465</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -11997,13 +12021,13 @@
         <v>85</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>85</v>
+        <v>624</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12021,16 +12045,16 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>85</v>
+        <v>625</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12051,20 +12075,282 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>534</v>
+        <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>535</v>
+        <v>469</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS75" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS76" t="s" s="2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS77" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS75">
+  <autoFilter ref="A1:AS77">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12074,7 +12360,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -950,7 +950,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lommo-45-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {null}</t>
+lommo-45-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {true}</t>
   </si>
   <si>
     <t>1480: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if Not NULL</t>
@@ -987,7 +987,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lommo-45-1480-1:If (undefined) is Not NULL then fixed value http://loinc.org {null}</t>
+lommo-45-1480-1:If Not NULL then fixed value http://loinc.org {true}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org if Not NULL</t>
@@ -1036,7 +1036,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lommo-45-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {null}</t>
+lommo-45-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {true}</t>
   </si>
   <si>
     <t>1480-2: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) if Not NULL</t>
@@ -1064,7 +1064,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lommo-45-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {null}</t>
+lommo-45-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {true}</t>
   </si>
   <si>
     <t>1480-3: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) if Not NULL</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3097" uniqueCount="620">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -843,6 +843,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -853,29 +875,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1428,37 +1428,6 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>2109: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>2110: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t>2111: target not supported</t>
-  </si>
-  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1620,7 +1589,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologySpecimen)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyMycologySpecimen)
 </t>
   </si>
   <si>
@@ -2305,12 +2274,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS77"/>
+  <dimension ref="A1:AS74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5254,7 +5223,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>267</v>
+        <v>85</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5272,16 +5241,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5306,28 +5275,28 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5335,13 +5304,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>262</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5385,7 +5354,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5403,10 +5372,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5439,7 +5408,7 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>85</v>
+        <v>275</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>85</v>
@@ -5457,10 +5426,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -8268,14 +8237,16 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>439</v>
@@ -8325,11 +8296,9 @@
         <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>85</v>
       </c>
@@ -8347,22 +8316,22 @@
         <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L47" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="N47" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8387,13 +8356,11 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8411,7 +8378,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8420,13 +8387,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>446</v>
+        <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8438,64 +8405,62 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>448</v>
+        <v>138</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>450</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>85</v>
+        <v>461</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8520,13 +8485,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8544,22 +8509,22 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>446</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>457</v>
+        <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8571,31 +8536,29 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>450</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>85</v>
       </c>
@@ -8604,7 +8567,7 @@
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>96</v>
@@ -8613,22 +8576,22 @@
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8677,25 +8640,25 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>446</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8704,27 +8667,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>450</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8738,7 +8701,7 @@
         <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>85</v>
@@ -8750,17 +8713,15 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>85</v>
       </c>
@@ -8784,11 +8745,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8806,7 +8769,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8815,13 +8778,13 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>467</v>
+        <v>85</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>468</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8833,38 +8796,38 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>85</v>
+        <v>489</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>138</v>
+        <v>490</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>471</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -8879,16 +8842,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8913,13 +8876,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>189</v>
+        <v>486</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8937,13 +8900,13 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -8964,27 +8927,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>478</v>
+        <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8995,7 +8958,7 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>96</v>
@@ -9007,20 +8970,18 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -9068,13 +9029,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -9083,39 +9044,39 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>85</v>
+        <v>509</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>85</v>
+        <v>513</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9138,16 +9099,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>515</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9173,13 +9134,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>497</v>
+        <v>85</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>498</v>
+        <v>85</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9197,7 +9158,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9224,27 +9185,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>502</v>
+        <v>522</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9255,7 +9216,7 @@
         <v>83</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>85</v>
@@ -9267,19 +9228,19 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>184</v>
+        <v>524</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9304,13 +9265,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>509</v>
+        <v>85</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9328,19 +9289,19 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>107</v>
+        <v>529</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9358,10 +9319,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9372,10 +9333,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9389,7 +9350,7 @@
         <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>85</v>
@@ -9398,17 +9359,15 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>513</v>
+        <v>162</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>514</v>
+        <v>163</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9457,7 +9416,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>512</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9469,53 +9428,53 @@
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>517</v>
+        <v>85</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>518</v>
+        <v>85</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>519</v>
+        <v>85</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>520</v>
+        <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>521</v>
+        <v>85</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>522</v>
+        <v>166</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>523</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -9527,16 +9486,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>525</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>526</v>
+        <v>142</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>527</v>
+        <v>168</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>528</v>
+        <v>144</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9586,19 +9545,19 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>524</v>
+        <v>172</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9613,31 +9572,31 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>529</v>
+        <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>531</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>532</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9650,25 +9609,25 @@
         <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>534</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>537</v>
+        <v>144</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>538</v>
+        <v>150</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9717,7 +9676,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9729,7 +9688,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>539</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9747,10 +9706,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>541</v>
+        <v>138</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9761,10 +9720,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9787,13 +9746,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>162</v>
+        <v>540</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>163</v>
+        <v>541</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>164</v>
+        <v>542</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9844,7 +9803,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>165</v>
+        <v>539</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9853,10 +9812,10 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9874,10 +9833,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>85</v>
+        <v>544</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>166</v>
+        <v>545</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9888,21 +9847,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9914,17 +9873,15 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>141</v>
+        <v>540</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>142</v>
+        <v>547</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9973,19 +9930,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>172</v>
+        <v>546</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -10003,10 +9960,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>85</v>
+        <v>544</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>166</v>
+        <v>549</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10017,45 +9974,45 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>545</v>
+        <v>85</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>144</v>
+        <v>553</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>150</v>
+        <v>554</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10080,13 +10037,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>85</v>
+        <v>555</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>85</v>
+        <v>556</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10104,19 +10061,19 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10131,13 +10088,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>85</v>
+        <v>557</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>85</v>
+        <v>558</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>138</v>
+        <v>470</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10148,10 +10105,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10162,7 +10119,7 @@
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>85</v>
@@ -10174,16 +10131,20 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>550</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10207,13 +10168,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>564</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10231,16 +10192,16 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>553</v>
+        <v>85</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10258,13 +10219,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>557</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>555</v>
+        <v>470</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10275,10 +10236,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10301,16 +10262,18 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10358,7 +10321,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10367,7 +10330,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>553</v>
+        <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10388,10 +10351,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>554</v>
+        <v>85</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10402,10 +10365,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10428,20 +10391,16 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
@@ -10465,13 +10424,13 @@
         <v>85</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>565</v>
+        <v>85</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>566</v>
+        <v>85</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10489,7 +10448,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10516,13 +10475,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>480</v>
+        <v>575</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10533,10 +10492,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10556,23 +10515,21 @@
         <v>85</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>184</v>
+        <v>577</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10596,13 +10553,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>574</v>
+        <v>85</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>575</v>
+        <v>85</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10620,7 +10577,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10647,13 +10604,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>480</v>
+        <v>582</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10664,10 +10621,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10678,7 +10635,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10687,21 +10644,21 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10749,13 +10706,13 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
@@ -10779,10 +10736,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10793,10 +10750,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10807,7 +10764,7 @@
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10816,19 +10773,23 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>162</v>
+        <v>524</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
       </c>
@@ -10876,13 +10837,13 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
@@ -10906,10 +10867,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>554</v>
+        <v>594</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10920,10 +10881,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10934,7 +10895,7 @@
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>85</v>
@@ -10943,20 +10904,18 @@
         <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>587</v>
+        <v>162</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>588</v>
+        <v>163</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
@@ -11005,19 +10964,19 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>586</v>
+        <v>165</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>85</v>
@@ -11035,10 +10994,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>591</v>
+        <v>85</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>592</v>
+        <v>166</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11049,14 +11008,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -11072,19 +11031,19 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>594</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>595</v>
+        <v>142</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>596</v>
+        <v>168</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>597</v>
+        <v>144</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11134,7 +11093,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>593</v>
+        <v>172</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11146,7 +11105,7 @@
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11164,10 +11123,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>591</v>
+        <v>85</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>598</v>
+        <v>166</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11178,14 +11137,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11198,25 +11157,25 @@
         <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>534</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>600</v>
+        <v>536</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>601</v>
+        <v>537</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>602</v>
+        <v>144</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>603</v>
+        <v>150</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11265,7 +11224,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>599</v>
+        <v>538</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11277,7 +11236,7 @@
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11295,10 +11254,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>604</v>
+        <v>85</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>605</v>
+        <v>138</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11309,10 +11268,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11320,7 +11279,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>95</v>
@@ -11332,19 +11291,23 @@
         <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>163</v>
+        <v>600</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11368,13 +11331,13 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>85</v>
+        <v>603</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11392,10 +11355,10 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>165</v>
+        <v>599</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>95</v>
@@ -11404,7 +11367,7 @@
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11419,16 +11382,16 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>85</v>
+        <v>286</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>166</v>
+        <v>287</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>85</v>
+        <v>288</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>85</v>
@@ -11436,21 +11399,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11459,21 +11422,23 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>141</v>
+        <v>440</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>142</v>
+        <v>606</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>168</v>
+        <v>607</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11521,19 +11486,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>172</v>
+        <v>605</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11548,62 +11513,62 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>85</v>
+        <v>609</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>85</v>
+        <v>448</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>166</v>
+        <v>449</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>85</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>545</v>
+        <v>85</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>546</v>
+        <v>611</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>547</v>
+        <v>612</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>144</v>
+        <v>613</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11628,13 +11593,13 @@
         <v>85</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>85</v>
+        <v>614</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11652,19 +11617,19 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>548</v>
+        <v>610</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>85</v>
@@ -11682,10 +11647,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>138</v>
+        <v>459</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11696,21 +11661,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>85</v>
+        <v>461</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -11719,22 +11684,22 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>610</v>
+        <v>462</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>611</v>
+        <v>463</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>612</v>
+        <v>464</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>281</v>
+        <v>465</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11759,13 +11724,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>496</v>
+        <v>189</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>613</v>
+        <v>466</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>283</v>
+        <v>467</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11783,13 +11748,13 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>85</v>
@@ -11810,27 +11775,27 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>614</v>
+        <v>468</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>286</v>
+        <v>469</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>287</v>
+        <v>470</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
-        <v>85</v>
+        <v>471</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11841,7 +11806,7 @@
         <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>85</v>
@@ -11850,22 +11815,22 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>440</v>
+        <v>86</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>618</v>
+        <v>527</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>444</v>
+        <v>528</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11914,13 +11879,13 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>85</v>
@@ -11941,416 +11906,23 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>619</v>
+        <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>448</v>
+        <v>530</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>449</v>
+        <v>531</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS75" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS76" t="s" s="2">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS77" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS77">
+  <autoFilter ref="A1:AS74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12360,7 +11932,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
